--- a/Tables/test al.xlsx
+++ b/Tables/test al.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\1_CV_test\H_System\Tables\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C592BFE-721C-4BB8-A9D3-D4202373DB6E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{04996465-8117-4574-938B-867F98EAE7D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{28AEAAB6-F9A9-49EC-9722-DA7FED8D2F54}"/>
   </bookViews>
@@ -39,23 +39,14 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="16">
   <si>
     <t>No. de control</t>
   </si>
   <si>
-    <t>Estatus</t>
-  </si>
-  <si>
     <t>9°A</t>
   </si>
   <si>
-    <t>ACREDITADO</t>
-  </si>
-  <si>
-    <t>NO ACREDITADO</t>
-  </si>
-  <si>
     <t>Merari Jocelyn Olivares Miranda</t>
   </si>
   <si>
@@ -93,12 +84,18 @@
   </si>
   <si>
     <t>Alfonzo Ruiz Collote</t>
+  </si>
+  <si>
+    <t>Calificacion Regualar</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.0"/>
+  </numFmts>
   <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -144,7 +141,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -152,6 +149,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -538,10 +542,9 @@
   <dimension ref="A1:D13"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="10.109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.77734375" bestFit="1" customWidth="1"/>
+    <col min="1" max="2" width="13.21875" customWidth="1"/>
     <col min="3" max="3" width="6.109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.5546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="16.5546875" style="5" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
@@ -549,41 +552,41 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" ht="57.6" x14ac:dyDescent="0.3">
+        <v>7</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A2" s="2">
         <v>323030001</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" ht="57.6" x14ac:dyDescent="0.3">
+        <v>1</v>
+      </c>
+      <c r="D2" s="3">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A3" s="2">
         <v>323030001</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>4</v>
+        <v>1</v>
+      </c>
+      <c r="D3" s="3">
+        <v>6</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
@@ -591,13 +594,13 @@
         <v>323030040</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>3</v>
+        <v>1</v>
+      </c>
+      <c r="D4" s="3">
+        <v>8</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
@@ -605,41 +608,41 @@
         <v>323003010</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
+        <v>1</v>
+      </c>
+      <c r="D5" s="3">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A6" s="2">
         <v>323000511</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
+        <v>1</v>
+      </c>
+      <c r="D6" s="3">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7" s="2">
         <v>3230345</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>4</v>
+        <v>1</v>
+      </c>
+      <c r="D7" s="3">
+        <v>6</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
@@ -647,41 +650,41 @@
         <v>3420365</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
+        <v>1</v>
+      </c>
+      <c r="D8" s="3">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9" s="2">
         <v>3230316</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
+        <v>1</v>
+      </c>
+      <c r="D9" s="3">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A10" s="2">
         <v>3230678</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>3</v>
+        <v>1</v>
+      </c>
+      <c r="D10" s="3">
+        <v>10</v>
       </c>
     </row>
     <row r="11" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
@@ -689,41 +692,41 @@
         <v>3245671</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+        <v>1</v>
+      </c>
+      <c r="D11" s="3">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A12" s="2">
         <v>3520586</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
+        <v>1</v>
+      </c>
+      <c r="D12" s="3">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A13" s="2">
         <v>1527440</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="D13" s="2" t="s">
-        <v>4</v>
+        <v>1</v>
+      </c>
+      <c r="D13" s="3">
+        <v>6</v>
       </c>
     </row>
   </sheetData>
